--- a/ExelData/Apparel_Armor_Balancing.xlsx
+++ b/ExelData/Apparel_Armor_Balancing.xlsx
@@ -5101,13 +5101,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="3">
         <f>ROUND((E10+D10*VLOOKUP(C10,Constants!$A$6:$G$11,2,0))*Constants!$B$2,2)</f>
@@ -5207,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1</v>
@@ -6320,10 +6320,10 @@
         <v>0.15</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>0.35</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0.45</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0.25</v>
@@ -12299,13 +12299,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="3">
         <f>ROUND((E21+D21*VLOOKUP(C21,Constants!$A$6:$G$11,2,0))*Constants!$B$2,2)</f>
@@ -12355,7 +12355,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>1</v>
@@ -12402,13 +12402,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0</v>
@@ -12455,16 +12455,16 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H24" s="3">
         <f>ROUND((E24+D24*VLOOKUP(C24,Constants!$A$6:$G$11,2,0))*Constants!$B$2,2)</f>
